--- a/assets/constructions/examples/ctd_mie_gears.xlsx
+++ b/assets/constructions/examples/ctd_mie_gears.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,26 @@
       <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>releasepack</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
         </is>
       </c>
     </row>
@@ -651,6 +671,20 @@
           <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
         </is>
       </c>
+      <c r="AB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>500.29</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>43966.79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,7 +694,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GMGE5N25W32-50-2U</t>
+          <t>GMGE3S125W142-315-3U</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -670,38 +704,36 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>H6</t>
-        </is>
-      </c>
+        <v>31.75</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>31</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29</v>
+      </c>
       <c r="J3" t="n">
-        <v>116</v>
+        <v>146.05</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>7.11</v>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -709,17 +741,17 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2U</t>
+          <t>3U</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>HB-25</t>
+          <t>HB-31.75</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>VARGUS_1/4U_GM</t>
+          <t>VARGUS_3/8U_GM</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,8 +767,22 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
-        </is>
+          <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>642</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>56420.63</v>
       </c>
     </row>
     <row r="4">
@@ -747,7 +793,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GMGE4S100W125-197-2U</t>
+          <t>GME5N32W35-80-3UM1-M1.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -757,38 +803,32 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>31.75</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>H6</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>90</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" t="n">
-        <v>55</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>17</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -796,17 +836,17 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2U</t>
+          <t>3U</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>HB-25.4</t>
+          <t>HB-35</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>VARGUS_1/4U_GM</t>
+          <t>VARGUS_3/8U_GM</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -822,9 +862,15 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
-        </is>
-      </c>
+          <t>2021 / Gear Milling_RUSSIAN_[270616] web .pdf</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -834,7 +880,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GME5N32W35-80-3UM1-M1.5</t>
+          <t>GMGE5N25W32-50-2U</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -844,27 +890,33 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
@@ -877,17 +929,17 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3U</t>
+          <t>2U</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>HB-35</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>VARGUS_3/8U_GM</t>
+          <t>VARGUS_1/4U_GM</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -903,8 +955,22 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021 / Gear Milling_RUSSIAN_[270616] web .pdf</t>
-        </is>
+          <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>413.46</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>36335.94</v>
       </c>
     </row>
     <row r="6">
@@ -915,7 +981,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GMGE3S125W142-315-3U</t>
+          <t>GMGE4S100W125-197-2U</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -925,36 +991,38 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>31.75</v>
       </c>
       <c r="F6" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>25.4</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>34</v>
-      </c>
-      <c r="I6" t="n">
-        <v>29</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>146.05</v>
+        <v>115</v>
       </c>
       <c r="K6" t="n">
-        <v>7.11</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>25.6</v>
+        <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -962,17 +1030,17 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3U</t>
+          <t>2U</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>HB-31.75</t>
+          <t>HB-25.4</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>VARGUS_3/8U_GM</t>
+          <t>VARGUS_1/4U_GM</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -990,6 +1058,20 @@
         <is>
           <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>531.58</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>46716.63</v>
       </c>
     </row>
   </sheetData>
